--- a/cardinalidad BD para modelos backend.xlsx
+++ b/cardinalidad BD para modelos backend.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\DSI115_Proyecto_UES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\DSI115_Proyecto_UES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0D197AE-4ECD-4952-BEEA-6C47ECFA94B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5792D6-CD10-4ED9-A47B-12384E2663BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{5688EC65-31DB-491F-8478-DB82F70C6C37}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5688EC65-31DB-491F-8478-DB82F70C6C37}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -426,7 +423,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,7 +769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -791,9 +788,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -829,58 +823,56 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1196,27 +1188,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4C369D-FB36-41A0-A9E0-7B88CC2C0EBE}">
   <dimension ref="A1:U42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="10" t="s">
         <v>8</v>
@@ -1235,8 +1227,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -1245,10 +1237,10 @@
       <c r="C2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="40" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -1258,18 +1250,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="36"/>
+    <row r="3" spans="1:21" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="43"/>
       <c r="B3" s="13" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="39"/>
+      <c r="E3" s="41"/>
       <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
@@ -1277,8 +1269,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="43"/>
       <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
@@ -1286,8 +1278,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="43"/>
       <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
@@ -1295,33 +1287,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="36"/>
-      <c r="B6" s="29" t="s">
+    <row r="6" spans="1:21" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="43"/>
+      <c r="B6" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="21" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
-      <c r="B7" s="34" t="s">
+    <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="44"/>
+      <c r="B7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32"/>
-    </row>
-    <row r="10" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+    </row>
+    <row r="10" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="10" t="s">
         <v>8</v>
@@ -1357,8 +1349,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="40" t="s">
+    <row r="11" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="37" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="12" t="s">
@@ -1367,10 +1359,10 @@
       <c r="C11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="37" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -1379,10 +1371,10 @@
       <c r="G11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="47" t="s">
+      <c r="I11" s="34" t="s">
         <v>27</v>
       </c>
       <c r="J11" s="2" t="s">
@@ -1391,10 +1383,10 @@
       <c r="K11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="50" t="s">
+      <c r="L11" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="N11" s="44" t="s">
+      <c r="N11" s="45" t="s">
         <v>77</v>
       </c>
       <c r="O11" s="2" t="s">
@@ -1403,7 +1395,7 @@
       <c r="P11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="S11" s="44" t="s">
+      <c r="S11" s="45" t="s">
         <v>88</v>
       </c>
       <c r="T11" s="2" t="s">
@@ -1413,47 +1405,47 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A12" s="41"/>
+    <row r="12" spans="1:21" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A12" s="38"/>
       <c r="B12" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="41"/>
+      <c r="E12" s="38"/>
       <c r="F12" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I12" s="48"/>
+      <c r="I12" s="35"/>
       <c r="J12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="26"/>
-      <c r="M12" s="51" t="s">
+      <c r="L12" s="23"/>
+      <c r="M12" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="N12" s="44"/>
+      <c r="N12" s="45"/>
       <c r="O12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q12" s="53" t="s">
+      <c r="Q12" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="R12" s="53"/>
-      <c r="S12" s="44"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="45"/>
       <c r="T12" s="2" t="s">
         <v>85</v>
       </c>
@@ -1461,46 +1453,46 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A13" s="41"/>
+    <row r="13" spans="1:21" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A13" s="38"/>
       <c r="B13" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="41"/>
+      <c r="E13" s="38"/>
       <c r="F13" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="48"/>
+      <c r="I13" s="35"/>
       <c r="J13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L13" s="21" t="s">
+      <c r="L13" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="N13" s="44"/>
+      <c r="N13" s="45"/>
       <c r="O13" s="2" t="s">
         <v>78</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q13" s="53"/>
-      <c r="R13" s="53" t="s">
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="S13" s="44"/>
+      <c r="S13" s="45"/>
       <c r="T13" s="2" t="s">
         <v>34</v>
       </c>
@@ -1508,43 +1500,43 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A14" s="41"/>
+    <row r="14" spans="1:21" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="38"/>
       <c r="B14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="27" t="s">
+      <c r="C14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="41"/>
+      <c r="E14" s="38"/>
       <c r="F14" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="H14" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="48"/>
+      <c r="I14" s="35"/>
       <c r="J14" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="L14" s="23"/>
-      <c r="N14" s="44"/>
+      <c r="L14" s="20"/>
+      <c r="N14" s="45"/>
       <c r="O14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="S14" s="44"/>
+      <c r="S14" s="45"/>
       <c r="T14" s="2" t="s">
         <v>86</v>
       </c>
@@ -1552,32 +1544,32 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="41"/>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="38"/>
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="41"/>
+      <c r="E15" s="38"/>
       <c r="F15" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="48"/>
-      <c r="J15" s="16" t="s">
+      <c r="G15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="35"/>
+      <c r="J15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="K15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="44"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="S15" s="44"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="S15" s="45"/>
       <c r="T15" s="2" t="s">
         <v>24</v>
       </c>
@@ -1585,38 +1577,38 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="41"/>
+    <row r="16" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="38"/>
       <c r="B16" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="42"/>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="39"/>
       <c r="F16" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="I16" s="49"/>
-      <c r="J16" s="16" t="s">
+      <c r="I16" s="36"/>
+      <c r="J16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="K16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N16" s="44"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-    </row>
-    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="42"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="39"/>
       <c r="B17" s="14"/>
-      <c r="C17" s="18"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C17" s="5"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="6" t="s">
         <v>8</v>
@@ -1646,8 +1638,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="43" t="s">
+    <row r="22" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="46" t="s">
         <v>30</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1656,10 +1648,10 @@
       <c r="C22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="53" t="s">
+      <c r="D22" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="44" t="s">
+      <c r="E22" s="45" t="s">
         <v>35</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -1668,7 +1660,7 @@
       <c r="G22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I22" s="44" t="s">
+      <c r="I22" s="45" t="s">
         <v>42</v>
       </c>
       <c r="J22" s="2" t="s">
@@ -1677,7 +1669,7 @@
       <c r="K22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M22" s="44" t="s">
+      <c r="M22" s="45" t="s">
         <v>43</v>
       </c>
       <c r="N22" s="2" t="s">
@@ -1687,35 +1679,35 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="43"/>
+    <row r="23" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="46"/>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="E23" s="44"/>
+      <c r="E23" s="45"/>
       <c r="F23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I23" s="44"/>
+      <c r="I23" s="45"/>
       <c r="J23" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L23" s="21" t="s">
+      <c r="L23" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="M23" s="44"/>
+      <c r="M23" s="45"/>
       <c r="N23" s="2" t="s">
         <v>38</v>
       </c>
@@ -1723,33 +1715,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="43"/>
+    <row r="24" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="46"/>
       <c r="B24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="52" t="s">
+      <c r="D24" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="44"/>
+      <c r="E24" s="45"/>
       <c r="F24" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H24" s="26"/>
-      <c r="I24" s="44"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="45"/>
       <c r="J24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M24" s="44"/>
+      <c r="M24" s="45"/>
       <c r="N24" s="2" t="s">
         <v>39</v>
       </c>
@@ -1757,33 +1749,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="43"/>
+    <row r="25" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="46"/>
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="27"/>
-      <c r="E25" s="44"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="45"/>
       <c r="F25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="44"/>
+      <c r="I25" s="45"/>
       <c r="J25" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L25" s="33" t="s">
+      <c r="L25" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="M25" s="44"/>
+      <c r="M25" s="45"/>
       <c r="N25" s="2" t="s">
         <v>40</v>
       </c>
@@ -1791,24 +1783,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="E26" s="44"/>
-      <c r="F26" s="16" t="s">
+    <row r="26" spans="1:15" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="E26" s="45"/>
+      <c r="F26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="33" t="s">
+      <c r="H26" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="I26" s="44"/>
+      <c r="I26" s="45"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="28" t="s">
+      <c r="L26" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="M26" s="44"/>
+      <c r="M26" s="45"/>
       <c r="N26" s="2" t="s">
         <v>29</v>
       </c>
@@ -1816,17 +1808,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E27" s="44"/>
-      <c r="F27" s="16" t="s">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E27" s="45"/>
+      <c r="F27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G27" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="44"/>
-      <c r="J27" s="16"/>
-      <c r="M27" s="44"/>
+      <c r="G27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="45"/>
+      <c r="J27" s="2"/>
+      <c r="M27" s="45"/>
       <c r="N27" s="2" t="s">
         <v>41</v>
       </c>
@@ -1834,8 +1826,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M28" s="44"/>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M28" s="45"/>
       <c r="N28" s="2" t="s">
         <v>44</v>
       </c>
@@ -1843,7 +1835,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="I31" s="2"/>
       <c r="J31" s="6" t="s">
         <v>8</v>
@@ -1852,8 +1844,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I32" s="45" t="s">
+    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I32" s="47" t="s">
         <v>54</v>
       </c>
       <c r="J32" s="2" t="s">
@@ -1863,7 +1855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A33" s="2"/>
       <c r="B33" s="6" t="s">
         <v>8</v>
@@ -1871,17 +1863,17 @@
       <c r="C33" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I33" s="46"/>
+      <c r="I33" s="48"/>
       <c r="J33" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K33" s="16" t="s">
+      <c r="K33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L33" s="22"/>
-    </row>
-    <row r="34" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="43" t="s">
+      <c r="L33" s="19"/>
+    </row>
+    <row r="34" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A34" s="46" t="s">
         <v>45</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -1890,10 +1882,10 @@
       <c r="C34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="33" t="s">
+      <c r="H34" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="I34" s="46"/>
+      <c r="I34" s="48"/>
       <c r="J34" s="2" t="s">
         <v>53</v>
       </c>
@@ -1901,15 +1893,15 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="43"/>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="46"/>
       <c r="B35" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I35" s="46"/>
+      <c r="I35" s="48"/>
       <c r="J35" s="2" t="s">
         <v>67</v>
       </c>
@@ -1917,18 +1909,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A36" s="43"/>
+    <row r="36" spans="1:12" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A36" s="46"/>
       <c r="B36" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="I36" s="46"/>
+      <c r="I36" s="48"/>
       <c r="J36" s="2" t="s">
         <v>68</v>
       </c>
@@ -1936,56 +1928,56 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="43"/>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="46"/>
       <c r="B37" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="I37" s="46"/>
-      <c r="J37" s="16" t="s">
+      <c r="C37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I37" s="48"/>
+      <c r="J37" s="2" t="s">
         <v>69</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="43"/>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="46"/>
       <c r="B38" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="I38" s="46"/>
-      <c r="J38" s="16" t="s">
+      <c r="C38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I38" s="48"/>
+      <c r="J38" s="2" t="s">
         <v>70</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="43"/>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="46"/>
       <c r="B39" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="I39" s="46"/>
-      <c r="J39" s="16" t="s">
+      <c r="C39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="48"/>
+      <c r="J39" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="43"/>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="46"/>
       <c r="B40" s="2" t="s">
         <v>4</v>
       </c>
@@ -1993,8 +1985,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="43"/>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="46"/>
       <c r="B41" s="2" t="s">
         <v>50</v>
       </c>
@@ -2002,8 +1994,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="43"/>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="46"/>
       <c r="B42" s="2" t="s">
         <v>5</v>
       </c>
@@ -2013,11 +2005,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="E22:E27"/>
-    <mergeCell ref="N11:N16"/>
-    <mergeCell ref="S11:S15"/>
-    <mergeCell ref="M22:M28"/>
-    <mergeCell ref="I22:I27"/>
     <mergeCell ref="A34:A42"/>
     <mergeCell ref="I32:I39"/>
     <mergeCell ref="A22:A25"/>
@@ -2026,6 +2013,11 @@
     <mergeCell ref="A11:A17"/>
     <mergeCell ref="E11:E16"/>
     <mergeCell ref="A2:A7"/>
+    <mergeCell ref="E22:E27"/>
+    <mergeCell ref="N11:N16"/>
+    <mergeCell ref="S11:S15"/>
+    <mergeCell ref="M22:M28"/>
+    <mergeCell ref="I22:I27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
